--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,6 +801,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>128875251</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56671</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>208260</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Huggorm</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Vipera berus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Emmaboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>534126</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6276432</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Emmaboda</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vissefjärda</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826821</v>
       </c>
       <c r="B2" t="n">
-        <v>56600</v>
+        <v>56603</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>128875251</v>
       </c>
       <c r="B3" t="n">
-        <v>56671</v>
+        <v>56674</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826821</v>
       </c>
       <c r="B2" t="n">
-        <v>56603</v>
+        <v>56606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>128875251</v>
       </c>
       <c r="B3" t="n">
-        <v>56674</v>
+        <v>56677</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -899,6 +899,522 @@
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>129220448</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56603</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100092</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Större brunfladdermus</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Nyctalus noctula</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Schreber, 1774)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1951</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Emmaboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>534133</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6276539</v>
+      </c>
+      <c r="S4" t="n">
+        <v>50</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Emmaboda</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vissefjärda</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>1951 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 19 av 20 autoboxar mellan juni juli.</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jesper Östlund</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Jesper Östlund</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129220499</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56589</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>997</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Emmaboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>534133</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6276539</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Emmaboda</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vissefjärda</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>997 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 17 av 20 autoboxar mellan juni juli.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jesper Östlund</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jesper Östlund</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129220484</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56610</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Emmaboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>534133</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6276539</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Emmaboda</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vissefjärda</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>242 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 14 av 20 autoboxar mellan juni juli.</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jesper Östlund</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jesper Östlund</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129220507</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56608</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>205995</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Dvärgpipistrell</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Pipistrellus pygmaeus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(W.E.Leach, 1825)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Emmaboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>534133</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6276539</v>
+      </c>
+      <c r="S7" t="n">
+        <v>50</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Emmaboda</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vissefjärda</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-02</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>05:30</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>265 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 18 av 20 autoboxar mellan juni juli.</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jesper Östlund</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jesper Östlund</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826821</v>
       </c>
       <c r="B2" t="n">
-        <v>56606</v>
+        <v>56608</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>128875251</v>
       </c>
       <c r="B3" t="n">
-        <v>56677</v>
+        <v>56679</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129220448</v>
       </c>
       <c r="B4" t="n">
-        <v>56603</v>
+        <v>56605</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>129220499</v>
       </c>
       <c r="B5" t="n">
-        <v>56589</v>
+        <v>56591</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>129220484</v>
       </c>
       <c r="B6" t="n">
-        <v>56610</v>
+        <v>56612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>129220507</v>
       </c>
       <c r="B7" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129220499</v>
+        <v>129220484</v>
       </c>
       <c r="B5" t="n">
-        <v>56591</v>
+        <v>56612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,26 +1041,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>997 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 17 av 20 autoboxar mellan juni juli.</t>
+          <t>242 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 14 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129220484</v>
+        <v>129220499</v>
       </c>
       <c r="B6" t="n">
-        <v>56612</v>
+        <v>56591</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,26 +1170,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>997</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>242 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 14 av 20 autoboxar mellan juni juli.</t>
+          <t>997 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 17 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128826821</v>
       </c>
       <c r="B2" t="n">
-        <v>56608</v>
+        <v>56610</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -807,7 +807,7 @@
         <v>128875251</v>
       </c>
       <c r="B3" t="n">
-        <v>56679</v>
+        <v>56681</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -904,7 +904,7 @@
         <v>129220448</v>
       </c>
       <c r="B4" t="n">
-        <v>56605</v>
+        <v>56607</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129220484</v>
+        <v>129220499</v>
       </c>
       <c r="B5" t="n">
-        <v>56612</v>
+        <v>56593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,26 +1041,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>997</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>242 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 14 av 20 autoboxar mellan juni juli.</t>
+          <t>997 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 17 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129220499</v>
+        <v>129220484</v>
       </c>
       <c r="B6" t="n">
-        <v>56591</v>
+        <v>56614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,26 +1170,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>997 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 17 av 20 autoboxar mellan juni juli.</t>
+          <t>242 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 14 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1291,7 +1291,7 @@
         <v>129220507</v>
       </c>
       <c r="B7" t="n">
-        <v>56610</v>
+        <v>56612</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129220499</v>
+        <v>129220484</v>
       </c>
       <c r="B5" t="n">
-        <v>56593</v>
+        <v>56614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,26 +1041,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>997 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 17 av 20 autoboxar mellan juni juli.</t>
+          <t>242 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 14 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129220484</v>
+        <v>129220499</v>
       </c>
       <c r="B6" t="n">
-        <v>56614</v>
+        <v>56593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,26 +1170,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>997</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>242 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 14 av 20 autoboxar mellan juni juli.</t>
+          <t>997 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 17 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -1030,10 +1030,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129220484</v>
+        <v>129220499</v>
       </c>
       <c r="B5" t="n">
-        <v>56614</v>
+        <v>56593</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,26 +1041,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>997</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1132,7 +1132,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>242 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 14 av 20 autoboxar mellan juni juli.</t>
+          <t>997 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 17 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1159,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129220499</v>
+        <v>129220484</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>56614</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,26 +1170,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>997 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 17 av 20 autoboxar mellan juni juli.</t>
+          <t>242 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 14 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -904,7 +904,7 @@
         <v>129220448</v>
       </c>
       <c r="B4" t="n">
-        <v>56607</v>
+        <v>56610</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1033,7 +1033,7 @@
         <v>129220484</v>
       </c>
       <c r="B5" t="n">
-        <v>56614</v>
+        <v>56617</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
         <v>129220499</v>
       </c>
       <c r="B6" t="n">
-        <v>56593</v>
+        <v>56596</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1291,7 +1291,7 @@
         <v>129220507</v>
       </c>
       <c r="B7" t="n">
-        <v>56612</v>
+        <v>56615</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128826821</v>
+        <v>129220448</v>
       </c>
       <c r="B2" t="n">
-        <v>56610</v>
+        <v>56830</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,26 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100111</v>
+        <v>100092</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Trollpipistrell</t>
+          <t>Större brunfladdermus</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pipistrellus nathusii</t>
+          <t>Nyctalus noctula</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1951</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,13 +727,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>534062</v>
+        <v>534133</v>
       </c>
       <c r="R2" t="n">
-        <v>6276596</v>
+        <v>6276539</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -762,22 +762,22 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
+          <t>2025-07-02</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>05:30</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Två inspelningar</t>
+          <t>1951 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 19 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,10 +804,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128875251</v>
+        <v>128826821</v>
       </c>
       <c r="B3" t="n">
-        <v>56681</v>
+        <v>56833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -815,34 +815,51 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208260</v>
+        <v>100111</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Huggorm</t>
+          <t>Trollpipistrell</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Vipera berus</t>
+          <t>Pipistrellus nathusii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
+          <t>(A.Keyserling &amp; Bläsius, 1839)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>autobox</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Emmaboda, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>534126</v>
+        <v>534062</v>
       </c>
       <c r="R3" t="n">
-        <v>6276432</v>
+        <v>6276596</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,12 +886,27 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>00:00</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-08-14</t>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>00:00</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Två inspelningar</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,22 +921,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Hanna Bengtsson</t>
+          <t>Jesper Östlund</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Hanna Bengtsson</t>
+          <t>Jesper Östlund</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129220448</v>
+        <v>129220507</v>
       </c>
       <c r="B4" t="n">
-        <v>56610</v>
+        <v>56835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -912,26 +944,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100092</v>
+        <v>205995</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Större brunfladdermus</t>
+          <t>Dvärgpipistrell</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nyctalus noctula</t>
+          <t>Pipistrellus pygmaeus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(W.E.Leach, 1825)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1951</t>
+          <t>265</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -1003,7 +1035,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>1951 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 19 av 20 autoboxar mellan juni juli.</t>
+          <t>265 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 18 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1030,10 +1062,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129220484</v>
+        <v>129220499</v>
       </c>
       <c r="B5" t="n">
-        <v>56617</v>
+        <v>56816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1041,26 +1073,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>242</t>
+          <t>997</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1132,7 +1164,7 @@
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>242 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 14 av 20 autoboxar mellan juni juli.</t>
+          <t>997 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 17 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1159,10 +1191,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129220499</v>
+        <v>129220484</v>
       </c>
       <c r="B6" t="n">
-        <v>56596</v>
+        <v>56837</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1170,26 +1202,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>205998</v>
+        <v>206002</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Brunlångöra</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Plecotus auritus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>242</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1261,7 +1293,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>997 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 17 av 20 autoboxar mellan juni juli.</t>
+          <t>242 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 14 av 20 autoboxar mellan juni juli.</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1288,10 +1320,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129220507</v>
+        <v>128875251</v>
       </c>
       <c r="B7" t="n">
-        <v>56615</v>
+        <v>56905</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1299,54 +1331,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>205995</v>
+        <v>208260</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dvärgpipistrell</t>
+          <t>Huggorm</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pipistrellus pygmaeus</t>
+          <t>Vipera berus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(W.E.Leach, 1825)</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>265</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>registreringar</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>autobox</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Emmaboda, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>534133</v>
+        <v>534126</v>
       </c>
       <c r="R7" t="n">
-        <v>6276539</v>
+        <v>6276432</v>
       </c>
       <c r="S7" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1370,27 +1385,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-06-03</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>21:00</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-02</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>05:30</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>265 registreringar på 4 nätters inventering 2*2 nätter juni-juli. 10 autoboxar vid juni och 10 autoboxar i juli. Emmaboda 4:1 har gott om viloplatser för fladdermöss. Spelades in i 18 av 20 autoboxar mellan juni juli.</t>
+          <t>2025-08-14</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1405,15 +1405,112 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Jesper Östlund</t>
+          <t>Hanna Bengtsson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Jesper Östlund</t>
+          <t>Hanna Bengtsson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128875259</v>
+      </c>
+      <c r="B8" t="n">
+        <v>106812</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Emmaboda, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>533970</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6276514</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Emmaboda</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vissefjärda</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hanna Bengtsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 21184-2024 artfynd.xlsx
+++ b/artfynd/A 21184-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129220448</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -930,6 +940,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128826821</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1059,6 +1074,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129220507</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1188,6 +1208,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129220499</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1317,6 +1342,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129220484</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1414,6 +1444,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128875251</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1511,8 +1546,22 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128875259</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>